--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -613,7 +613,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -613,7 +613,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -613,7 +613,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -613,7 +613,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -499,7 +499,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>Las frases de cada artículo que el modelo de lenguaje (Claude Opus 5) localizó de forma automática, buscando expresiones, para cada dominio o tema de riesgo de sesgo, y que puso como comentario en las casillas de los formularios. Sirven para buscar en el artículo, no para sostener un juicio.</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2.7. Lo que sostiene cada juicio está en S18. Un tema sin frases quiere decir que el buscador no encontró la expresión, no que el artículo no trate el asunto.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -613,7 +617,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$E$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$E$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Las frases de cada artículo que el modelo de lenguaje (Claude Opus 5) localizó de forma automática, buscando expresiones, para cada dominio o tema de riesgo de sesgo, y que puso como comentario en las casillas de los formularios. Sirven para buscar en el artículo, no para sostener un juicio.</t>
+          <t>Las frases de cada artículo que el modelo de lenguaje (Claude Opus 5) localizó de forma automática, buscando expresiones, para cada dominio o tema de riesgo de sesgo, y que puso como comentario en las casillas de los formularios. Sirven para buscar en el artículo, no para sostener un juicio. Solo trae los 9 estudios que tienen juicio en S18; las frases cosechadas para cualquier otro estudio no se incluyen.</t>
         </is>
       </c>
     </row>
@@ -521,103 +528,110 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>229 filas de datos</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>174 filas de datos</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>dominio</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: dominio</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: n</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>frase</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: frase</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -632,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -643,27 +657,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>dominio</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>frase</t>
         </is>
@@ -2337,7 +2351,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2352,46 +2366,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>...e(differential,typicalsymptoms, andQoLdomain)andanincreasedvolumeofvoidsafter14days oftherapy. Bacteriophagetherapyhasbeendescribedinseveralclinicaltri- als,demonstratingpromiseintreatingUTIscausedbyantibiotic- resistant uropathogens. In a randomized, placebo-controlled, double-blindstudy,Leitneretal.[19]haveshownthatintravesical bacteriophagetherapywithPyophagewasnotlesseffectivethan standardantibiotictreatmentbutwasalsonotmoreeffectivethan placebo.Inacasereportofa56-year-oldmanwithre...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>...netobacterbaumannii biofilminahumanurinemodel.MicrobDrugResist2021;27:25–35. [19] LeitnerL,UjmajuridzeA,ChanishviliN,etal.Intravesicalbacteriophages fortreatingurinarytractinfectionsinpatientsundergoingtransurethral resectionoftheprostate:Arandomised,placebo-controlled,double-blind clinicaltrial.LancetInfectDis2021;21:427–436. 4elbaT .spuorg4nitnemtaertfo)B(syad41dna)A(syad7taenilesabmorfycneuqerfyranirudna,enirufoemulovdediov,airutycokuellevelfonosirapmocehT -laksurK(p VIpuorG +egahpa...</t>
+          <t>...Open Forum Infectious Diseases MAJOR ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center Hadil Onallah,1,2Ronen Hazan,2,3and Ran Nir-Paz,1,2,4for the Israeli Phage Therapy Center (IPTC) Study Teama 1Faculty of Medici...</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2406,42 +2416,46 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>...erapy courses were given to 18 patients by the IPTC. In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen. Clearly, establishing an Israeli phage center has led to an increased demand for compassionate use of phages with favorable outcomes for many previously failed infections. As clinical trials are still lacking, publishing patient data from cohort studies is pertinent to establish clinical indications, protocols, and success and failure r...</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>...al,typicalsymptoms, andQoLdomain)andanincreasedvolumeofvoidsafter14days oftherapy. Bacteriophagetherapyhasbeendescribedinseveralclinicaltri- als,demonstratingpromiseintreatingUTIscausedbyantibiotic- resistant uropathogens. In a randomized, placebo-controlled, double-blindstudy,Leitneretal.[19]haveshownthatintravesical bacteriophagetherapywithPyophagewasnotlesseffectivethan standardantibiotictreatmentbutwasalsonotmoreeffectivethan placebo.Inacasereportofa56-year-oldmanwithrecurrentUTI, Terwilli...</t>
+          <t>...age matching process were the main reasons for failure. sisted of 2 treatment cycles. The follow-up period varied No major side effects were reported by the patients during from 1 month and up to 3 years. Of the 20 patients, 2 are cur- the compassionate use phage treatment. One patient (treat- rently undergoing treatment based on their protocol, and no ments 6 and 8) reported headaches 1 hour after each intrave- outcome evaluation is available for them yet. Among the re- nous treatment, and 2...</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2456,56 +2470,48 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>...and then using antibiotics to which there is no theeffluxpumpmechanism,achievedbythebindingoflyticbac- resistance could be an effective treatment regimen. There is a teriophagestothereceptor-bindingsitesontheoutermembrane need for larger, placebo-controlled clinical studies to explore of MDRB.[8] Valério et al.[25] have reported that the combina- thisarea. tionofphageandciprofloxacinatsublethalconcentrationssig- nificantly decreased the levels of E. coli bacteriuria compared Acknowledgments w...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>...aumannii biofilminahumanurinemodel.MicrobDrugResist2021;27:25–35. [19] LeitnerL,UjmajuridzeA,ChanishviliN,etal.Intravesicalbacteriophages fortreatingurinarytractinfectionsinpatientsundergoingtransurethral resectionoftheprostate:Arandomised,placebo-controlled,double-blind clinicaltrial.LancetInfectDis2021;21:427–436. 4elbaT .spuorg4nitnemtaertfo)B(syad41dna)A(syad7taenilesabmorfycneuqerfyranirudna,enirufoemulovdediov,airutycokuellevelfonosirapmocehT -laksurK(p VIpuorG +egahpatxeS(IIIpuorG IIpuo...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2515,24 +2521,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>...res. At 90% power and a bacteriophage(Sextaphage)therapyalone;groupII:combination 5%2-sidedsignificancelevel,weestimatedasamplesizeof44in- ofbacteriophages(Sextaphage)andfurazidin;groupIII:combina- dividualsineachgroup.Takingaccountofthe20%dropoutrate, tionbacteriophage(Sextaphage)andfurazidinwithcefixime;and werequired45participantsineachgroup,givingatotalsample groupIVreceivedfurazidinandcefixime(withoutbacteriophage). size of 180. The treatment effects were also compared with the...</t>
+          <t>...ical cultures together with positron emission The phage sourcing process, including phage isolation, charac- tomography/magnetic resonance imaging negative for infec- terization, and full genome sequence, in addition to tion. Remission was defined as the absence of clinical signs of 2 • OFID • Onallah et al Downloaded from academic.oup.com/ofid/article/10/5/ofad221/7133195 by guest on 20 August 2026A B C Figure 1. A, Phage request registry and processing workflow at the Israeli Phage Therapy Cente...</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2545,17 +2551,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2568,30 +2574,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>...TC is currently the leading therapy for patients and their specific bacterial infections [8–14]. and only center in Israel focusing on phage therapy. It provides all services related to phage therapy—phage discovery and charac- terization, phage susceptibility and matching tests, authorization of Received 05 January 2023; editorial decision 17 April 2023; accepted 19 April 2023; pub- lished online 20 April 2023 treatments for patients from Israel and abroad, and delivering and aMembers of the IP...</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2606,19 +2616,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>...eudomonasaeruginosa,enteropatho- Atotalof217femalepatientswithchronicrecurrentcystitiswere genic E. coli, and Klebsiella pneumoniae. The treatment included recruitedforthestudyfromJune2020toDecember2022.During both monotherapy with bacteriophage cocktail (Sextaphage) theenrollmentperiod,39womenwereexcludedfromthestudy (30 mL, orally, 6 times a day) and its combination with cefixime for various reasons, including urethral catheterization (n = 7), Table1 Baselineclinicalanddemographiccharact...</t>
+          <t>...at The Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing framework previously published by the group [23, 24]. In all Israeli centers, clinical microbiology laboratories follow Phage susceptibility testing was performed in several steps, pathogen identification using matrix-assisted laser desorp- using at least 3 methods [24]. First, a spot assay screen, using tion/ionization–time of flight (MALDI-TOF) and the Vitek all relevant phag...</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2633,46 +2643,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>...multidrug- resistant microorganisms are crucial.[16] Bacteriophage therapy isconsideredapotentiallyeffectivemethodfortreatingbacterial infectionscausedbymultidrug-resistantpathogens.[17] According to our data, the combination of a bacteriophage cocktail (Sextaphage) with antibiotics (furazidin + cefixime or furazidinalone)hadamoresignificanteffectontheclinicalsymp- tomsofchronicrecurrentcystitisthanbacteriophagemonother- apy.Inthehumanurinemodel,Grygorcewiczetal.[18]havedem- onstrated sim...</t>
+          <t>...hages in our phage bank, was performed [23]. system. All the strains (Israeli and abroad) that were submitted Phages that yielded clear plaques in this assay were picked for have undergone identification and sensitivity testing according a plaque-forming unit count. The third step was kinetic deter- to the routine clinical microbiology laboratory at the Hadassah mination of the efficacy of the phages with and without the rel- Medical Center. Pathogen identification of all isolates was car-...</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>...efixime or furazidinalone)hadamoresignificanteffectontheclinicalsymp- tomsofchronicrecurrentcystitisthanbacteriophagemonother- apy.Inthehumanurinemodel,Grygorcewiczetal.[18]havedem- onstrated similar effects of the combination of a bacteriophage cocktailandsomeoftheantibioticscommonlyusedforthetreatment ofUTI(sulfamethoxazole/trimethoprim,ciprofloxacin,levofloxacin, imipenem,andmeropenem)intheeradicationofbiofilmbiomassof Acinetobacterbaumannii. Thewomenwhoreceivedcombinationtherapyexperie...</t>
+          <t>...22. The following data were collected: patient Phage Therapy in Israel • OFID • 1 Downloaded from academic.oup.com/ofid/article/10/5/ofad221/7133195 by guest on 20 August 2026demographics, clinical indication, bacterial pathogen, and anti- susceptibility testing and phage-antibiotic kinetic assays, were biotic susceptibility of the pathogen. performed by the Israeli Phage Bank at The Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing fr...</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2687,19 +2697,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>...onofbacteriophagetherapywithantibioticsandbacte- riophagetreatmentaloneonrelievingclinicalsymptomsofchronicrecurrentcystitiscausedbymultidrug-resistantbacteria. Materials and methods: This clinical trial comparedthe treatment methods of 217female patientswith chronic recurrent cystitis causedbymultidrug-resistantbacteria,whowereinvestigatedfromJune2020toMay2023.Patientswereallocatedinto4groups: groupI:receivedbacteriophage(Sextaphage)therapyalone;groupII:receivedacombinationofbacteriophage...</t>
+          <t>...Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing framework previously published by the group [23, 24]. In all Israeli centers, clinical microbiology laboratories follow Phage susceptibility testing was performed in several steps, pathogen identification using matrix-assisted laser desorp- using at least 3 methods [24]. First, a spot assay screen, using tion/ionization–time of flight (MALDI-TOF) and the Vitek all relevant phages in ou...</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2714,46 +2724,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>...n placebo.Inacasereportofa56-year-oldmanwithrecurrentUTI, Terwilligeretal.[20]havedemonstratedthattheuseofabacterio- phagecocktailalongwithertapenemmayleadtocompletebacterial eradication and prevention of phage resistance. In another case, a 63-year-oldwomanwithrecurrentUTIcausedbymultidrug-resistant KlebsiellapneumoniaewassuccessfullytreatedbyBaoetal.[21]The combinationofsulfamethoxazole-trimethoprimandaphagecock- tail effectively treated the disease despite initial resistance to the ant...</t>
+          <t>...s was car- evant antibiotics. This step reveals also possible antagonistic or ried out using a MALDI-TOF mass spectrometer (bioMérieux, synergistic effects of phages and antibiotics. When the optical Marcy l’Etoile, France), and antibiotic susceptibility testing was density in this assay is below the detection threshold, due to ly- conducted utilizing the VITEK 2 system (bioMérieux) follow- sis, a colony-forming unit count was also performed to detect if ing the Clinical and Laboratory Standards I...</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>...ataavailability Alldatageneratedoranalyzedduringthisstudyareincludedinthis publishedarticle[anditssupplementaryinformationfiles]. References [1] WaldorffMS,BjerrumL,HolmA,etal.Influenceofantimicrobialresistance on the course of symptoms in female patients treated for uncomplicated cystitiscausedbyEscherichiacoli.Antibiotics(Basel)2022;11:188. [2] BaderMS,LoebM,BrooksAA.Anupdateonthemanagementofurinary tractinfectionsintheeraofantimicrobialresistance.PostgradMed2017; 129:242–258. [3] AngerJ...</t>
+          <t>...age requests and served as a clinical research file Astrid Military Hospital, Brussels, Belgium). for phage therapy cases (see Supplementary Form). Study data were collected and managed using REDCap electronic Patient Consent Statement and Ethics Approvals data capture tools hosted at the Hadassah Medical Center. For each patient, informed consent was obtained. Additionally, according to the regulations in Israel for each individual treat- Communication ment, a formal approval of the local...</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2768,46 +2778,46 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>...fintereststatement Abacteriophagecocktail,eitheraloneorincombinationwith Allauthorsdeclarethattheyhavenoconflictsofinterest. antibiotics, may improve clinical symptoms in women with chronicrecurrentcystitiscausedbymultidrug-resistantbacte- Fundingsource rialpathogens.Inadditiontosymptomimprovement,therapy with a phage cocktail may resensitize microbes to antibiotics. None. 130Authorcontributions DK:Researchdesign,writing,dataanalysis,projectdevelopment; NI:Editing,writing; GB:Editin...</t>
+          <t>...s data capture tools hosted at the Hadassah Medical Center. For each patient, informed consent was obtained. Additionally, according to the regulations in Israel for each individual treat- Communication ment, a formal approval of the local institutional review board Requests were sent mostly by physicians from different hospi- (IRB/ethics committee) and the Ministry of Health was neces- tals and health centers in Israel (91% of all requests), with 9% of sary for initiating compassionate therapy,...</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>...rated treatment in children with Received 7 July 2022 HOW THIS STUDY MIGHT AFFECT RESEARCH, Accepted 21 April 2023 CF infected with P. aeruginosa infection in their airways. PRACTICE OR POLICY Methods This single- arm, open- labelled, non- randomised trial will run for a maximum period of 36 months with up to ⇒ If our hypothesis is supported, our study will pave 10 participants. Adolescents (≥12 years and &lt;18 years of the way for the use of bacteriophages in children age) who continue...</t>
+          <t>...and the Ministry of Health was neces- tals and health centers in Israel (91% of all requests), with 9% of sary for initiating compassionate therapy, together with obtain- requests coming from abroad. All requests were sent initially to ing informed consent from each patient. Publication was done an infectious diseases specialist (R. N.-P.) at the Hadassah- upon the following Hadassah IRB approval numbers: 0420-12- Hebrew University Medical Center and then relayed to the lab- HMO, 0309-18-HMO...</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2822,19 +2832,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>...ome are known to affect multiple strains of the Design bacteria.28–30 The microbiota has been shown to be less This trial is designed as a small, pilot, single-a rm, open- affected by phages when compared with antibiotics31; labelled, non- randomised, safety and tolerability study this has been shown in both murine and human studies with a primary endpoint of tolerance towards endo- (adults and children).32 33 A trial performed in children bronchially instilled initial phage dose follo...</t>
+          <t>...withUTI[4]. ArecentlypublishedreviewonPTinUTIsummarized withregardtojurisdictionalclaimsin currentlyavailabledatasuggestingthatthismodeoftreatmentmaybeanattractiveoption publishedmapsandinstitutionalaffil- forthosepatients[5].Nevertheless,arandomized,placebo-controlled,double-blindclinical iations. trialofintravesicalPTfortreatingUTIinpatientsundergoingtransurethralresectionof theprostatewasnotfoundtobesuperiortoplacebobladderirrigation[6]. Therefore,new studiesandmoredataareneededtocl...</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2849,79 +2859,83 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>...ISTRY-MANUFACTURING-AND absorption viraemia of T3 phages after oral, trachéal and rectal 62 Teper A, Jaques A, Charlton B. Inhaled mannitol in patients with administration. Zentralblatt Fur Bakteriologie, Parasitenkunde, cystic fibrosis: a randomised open- label dose response trial. J Cyst Infektionskrankheiten Und Hygiene 1965;198:371–90. Fibros 2011;10:1–8. 38 Majewska J, Beta W, Lecion D, et al. Oral application of T4 phage 63 DELACOSTE P. Considerations on the treatment of common i...</t>
+          <t>...PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provided conclusive data confirming the real therapeutic valueofthetherapy. Therefore,thereisanurgentneedforawell-plannedclinicaltrialthat coulddeterminewhetherindeedPTcanofferareliableweaponagainstantibiotic-resistant b...</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>...in of intrabronchial and nebulised aggressive antibiotic treatment. This predisposes the patient the treatment of resistant bacterial infections based bacteriophage treatment to complications such as sensorineural hearing loss, renal on a compassionate use basis. in children with cystic impairment, hypersensitivity and the development of antibiotic fibrosis and Pseudomonas WHAT THIS STUDY ADDS resistance. Pseudomonas aeruginosa is one of the more aeruginosa. BMJ Open Resp common organisms wh...</t>
+          <t>...li, N.; Goderdzishvili, M.; Chkonia, I.; Rigvava, S.; Chkhotua, A.; Changashvili, G.; McCallin, S.; Schneider, M.P.; etal. Intravesicalbacteriophagesfortreatingurinarytractinfectionsinpatientsundergoing transurethralresectionoftheprostate:Arandomised,placebo-controlled,double-blindclinicaltrial.LancetInfect.Dis.2021,21, 427–436.[CrossRef] 7. Mie˛dzybrodzki,R.;Borysowski,J.;Weber-Da˛browska,B.;Fortuna,W.;Letkiewicz,S.;Szufnarowski,K.;Pawełczyk,Z.;Rogóz˙,P.; Kłak,M.;Wojtasik,E.;etal.Clin...</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>...its successful use in treating multidrug-resistantbacterialinfectionsarepublishedalmosteverymonth[9–17]. Like- wise, several reviews on PT are published each year. However, there is a growing gap between the expansion of PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provid...</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2931,176 +2945,160 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>...is includes methods such elimination rate constant Primary outcomes (safety and tolerance) obtained from the log transformed concentration-t ime Treatment success will be defined as the absence of the curve. Data of study participants that drop out of the following adverse events: study will be used up to the last available data point ► Fever &gt;38.5°C over three consecutive temporally before the drop- out date. related administration or three episodes of tempo- rally related fever abo...</t>
+          <t>...ArecentlypublishedreviewonPTinUTIsummarized withregardtojurisdictionalclaimsin currentlyavailabledatasuggestingthatthismodeoftreatmentmaybeanattractiveoption publishedmapsandinstitutionalaffil- forthosepatients[5].Nevertheless,arandomized,placebo-controlled,double-blindclinical iations. trialofintravesicalPTfortreatingUTIinpatientsundergoingtransurethralresectionof theprostatewasnotfoundtobesuperiortoplacebobladderirrigation[6]. Therefore,new studiesandmoredataareneededtoclarifythevalueofPTin...</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>...affects mucous, standard CF treatment (intravenous antibiotics, physiotherapy sweat and digestive enzyme production, and to be completed as inpatient for 10–14 days). Safety and is characterised by recurrent pulmonary tolerability will be defined as the absence of (1) fever infections, each of which requires aggres- above 38.5°C occurring within 1 hour of the administration sive antibiotic treatment. One of the most of the nebulised bacteriophage, (2) a 10% decline in common organisms that affect...</t>
+          <t>...s a growing gap between the expansion of PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provided conclusive data confirming the real therapeutic valueofthetherapy. Therefore,thereisanurgentneedforawell-plannedclinicaltrialthat coulddeterminewhetherindeedPTcanofferarelia...</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>...be less This trial is designed as a small, pilot, single-a rm, open- affected by phages when compared with antibiotics31; labelled, non- randomised, safety and tolerability study this has been shown in both murine and human studies with a primary endpoint of tolerance towards endo- (adults and children).32 33 A trial performed in children bronchially instilled initial phage dose followed by with diarrhoeal disease demonstrated that phages pass maintenance treatment via nebulisation. This st...</t>
+          <t>...erdzishvili, M.; Chkonia, I.; Rigvava, S.; Chkhotua, A.; Changashvili, G.; McCallin, S.; Schneider, M.P.; etal. Intravesicalbacteriophagesfortreatingurinarytractinfectionsinpatientsundergoing transurethralresectionoftheprostate:Arandomised,placebo-controlled,double-blindclinicaltrial.LancetInfect.Dis.2021,21, 427–436.[CrossRef] 7. Mie˛dzybrodzki,R.;Borysowski,J.;Weber-Da˛browska,B.;Fortuna,W.;Letkiewicz,S.;Szufnarowski,K.;Pawełczyk,Z.;Rogóz˙,P.; Kłak,M.;Wojtasik,E.;etal.Clinicalaspectsofphaget...</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>...n, isolation, purification, viability lised bacteriophage despite a reduction of dosing and testing and sterility data template. pretreatment with inhaled salbutamol.62 ► Bronchoscopy report. ► Lung function indices and anthropometric data Secondary outcomes (weight and height) will be obtained from standard- A reduction in sputum bacterial culture titres of P. aerugi- ised measurements and report available on the study nosa from pretreatment to day 7 of treatment. participants’ electronic me...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>...y has legislation, (3) National Health and Medical Research Council 2.6 times higher risk of death within 8 years Correspondence to guidelines for the ethical conduct of research. when compared with a child with CF who has Dr Jagdev Singh; Trial registration number Australia and New Zealand not been infected with the organism. These J agdev.s ingh@h ealth.n sw. Clinical Trial Registry (ACTRN12622000767707). gov.a u children also have a lower baseline weight Singh J, et al. BMJ Open Resp Res 20...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>...diagnosed immu- Patient and public involvement nosuppressive condition. None. ► Children that require ≥18 hours/day of non- invasive ventilatory support during admission. Study population ► A current diagnosis of allergic bronchopulmonary Inclusion criteria aspergillosis (ABPA). ► Adolescents (≥12 years and &lt;18 years of age) with CF. ► History of haemoptysis in the past 12 months before ► Positive sputum or bronchoalveolar lavage culture (P. study enrolment. aeruginosa) in more than 50% of sp...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>...Open Access Respiratory infection Single- arm, open- labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in children with cystic fibrosis and Pseudomonas aeruginosa Jagdev Singh ,1,2 Dominic A Fitzgerald,1,2 Adam Jaffe,3 Sharon Hunt,1 Jeremy J Barr,4 Jonathan Iredell,5,6 Hiran Selvadurai1,2 To cite: Singh J, Fitzgera...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3115,19 +3113,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>...pen- Introduction Cystic fibrosis (CF) is a multisystem condition labelled, safety and tolerability that is complicated by recurrent pulmonary infections requiring ⇒ Bacteriophages are demonstrating great potential in of intrabronchial and nebulised aggressive antibiotic treatment. This predisposes the patient the treatment of resistant bacterial infections based bacteriophage treatment to complications such as sensorineural hearing loss, renal on a compassionate use basis. in child...</t>
+          <t>...ed monovalent lysates of bacteriophagepreparationsofEscherichiacoli, Klebsiellapneumoniae, Enterococcusfaecalis or Pseudomonas aeruginosa based on phage typing (Tables 1 and 2). Phage lysates had concentrationsof106–108plaqueformingunit/mL(pfu/mL).Healthydonorsdidnotuse bacteriophagepreparations,buttheirserawereexaminedforthepresenceofantiphage antibodies against bacteriophage preparations E. coli phage coli 48/D1, K. pneumoniae phageKl16/30,E.faecalisphageEntc15/PandP.aeruginos...</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3142,69 +3140,69 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>...uring practice recommendations. The selected bacteriophage will be condition of the lungs, exocrine organs administered endo-b ronchially first under direct vision, followed and gastrointestinal tract that occurs in 1 in by two times a day nebulisation for 7 days in addition to 2500 births. This condition affects mucous, standard CF treatment (intravenous antibiotics, physiotherapy sweat and digestive enzyme production, and to be completed as inpatient for 10–14 days). Safety and is...</t>
+          <t>...ingphagetherapyandcontrolofhealthyindivid- ualswastestedwiththeplatephageneutralizationtest. TheAASresearchwasperformed accordingtothemethoddescribedearlier[8]. Undilutedanddilutedserafrom1:10to 1:1500weretested. Atotalof50µLofthephagewithatiterof1×106pfu/mLwereadded toeachserumdilution(450µL).Phagetitercontrolwasperformedbyadding50µLofthe phagewithatiterof1×106 pfu/mLto450µLofbroth. Themixturewasincubatedfor 30minat37◦C.Afterthistime,50µLofthemixtureweretakenandaddedto4.95mL ofco...</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>...ereadded toeachserumdilution(450µL).Phagetitercontrolwasperformedbyadding50µLofthe phagewithatiterof1×106 pfu/mLto450µLofbroth. Themixturewasincubatedfor 30minat37◦C.Afterthistime,50µLofthemixtureweretakenandaddedto4.95mL ofcoldbroth. Phagetiterwasexaminedatthebeginningofthephagereactionwiththe serumand,afterthe30minreaction,bythestandarddouble-agarlayermethod. Atotal of100µLofthemixtureand200µLofthebacterialstrainwereaddedto3mLof0.7% agarandpouredontoagarplates. Theplateswereincu...</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>...tions Pseudomonas This table was adapted from Abedon et al. These studies that have been cited may be in languages other than English and therefore are obtained from a summarised review article that has been published in English.69 Network Ethics committee (ethics approval number antipseudomonal antibiotics and/or is currently on 2022/ETH00241, version 3). Amendments will be noti- suppressive nebulised antibiotic treatment. fied to the approving ethics committee and is subject ► The latest c...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3219,46 +3217,46 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>...y (for bronchoalveolar gator. A severe unexpected side effect report will be only), IgG, IgA, IgM, phage neutralising antibodies); submitted to the Sydney Children’s Hospital Network blood sample (full blood count, renal and liver profile, Ethics committee. C reactive protein, blood culture, interleukin 6, TNFα, Ancillary and post- trial care will be provided by the IgG, IgA, IgM, nanoString RNA sequencing, phage Sydney Children Hospital Network. neutralising antibodies); stool sample (bacte...</t>
+          <t>...erimentsandanalyzeddata;R.M.analyzed data;M.Z˙.designedandperformedtheexperimentsandanalyzeddata;B.W.-D.wrotepartsofthe manuscript;A.G.conceivedthestudyandwrotethemanuscript.Allauthorshavereadandagreed tothepublishedversionofthemanuscript. Funding:Thisresearchreceivednoexternalfunding. InstitutionalReviewBoardStatement:Thestudywasconductedaccordingtotheguidelinesofthe DeclarationofHelsinki,andapprovedbytheBioethicsCommitteeattheWroclawMedicalUniversity (protocoltitle“Phageinactivati...</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>...the initial and final versions of the manuscript. All authors critically reviewed early and final versions of the participant (before administering the bacteriophage and manuscript. at the end of admission). Auditing of record keeping and Funding This study was funded by the Cure4CF Holckner Family Impact Grant and adherence to protocol will be based on the stipulation by The Team Simon Foundation for Cystic Fibrosis. the Sydney Children’s Hospital Network Ethics Committee. Competi...</t>
+          <t>...2023 A list of authors and their affiliations appears at the end of the paper Accepted: 19 April 2024 Published online: 4 June 2024 In contrast to the many reports of successful real-world cases of personalized bacteriophage therapy (BT), randomized controlled Check for updates trials of non-personalized bacteriophage products have not produced the expected results. Here we present the outcomes of a retrospective observational analysis of the first 100 consecutive cases of personalize...</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3273,42 +3271,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>...each bacteriophage API batch. The BT protocols that were suggested turing practices (GMP) certification, preclinical research (toxicity and to the treating physicians were based on the experiences of the George pharmacology) and conducting randomized controlled trials (RCTs). Eliava Institute of Bacteriophages, Microbiology and Virology (Eliava However, the handful of bacteriophage RCTs that have been performed Institute) in Tbilisi, Georgia (personal communications), and on the so far...</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>...Open Forum Infectious Diseases MAJOR ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center Hadil Onallah,1,2Ronen Hazan,2,3and Ran Nir-Paz,1,2,4for the Israeli Phage Therapy Center (IPTC) Study Teama 1Faculty of Medici...</t>
+          <t>...primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection types were involved. Evaluation of safety failure of eradication was observed in 43% (3/7) of patients...</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3323,19 +3325,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>...erapy courses were given to 18 patients by the IPTC. In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen. Clearly, establishing an Israeli phage center has led to an increased demand for compassionate use of phages with favorable outcomes for many previously failed infections. As clinical trials are still lacking, publishing patient data from cohort studies is pertinent to establish clinical indications, protocols, and success and failure r...</t>
+          <t>...me of their therapy (BT), the use of bacteriophages—the viruses of bacteria—to use in clinical practice. Of note, most selected cases concerned per- treat bacterial infections, was first applied by Félix d’Hérelle in 19192, sonalized BT as salvage therapy after standard antibiotic treatments and further developed and applied in the former Soviet Union. had failed. Quality and safety of the bacteriophage preparations were A recent systematic review confirmed that BT can generally be verified...</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3350,125 +3352,137 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>...age matching process were the main reasons for failure. sisted of 2 treatment cycles. The follow-up period varied No major side effects were reported by the patients during from 1 month and up to 3 years. Of the 20 patients, 2 are cur- the compassionate use phage treatment. One patient (treat- rently undergoing treatment based on their protocol, and no ments 6 and 8) reported headaches 1 hour after each intrave- outcome evaluation is available for them yet. Among the re- nous treatment, and 2...</t>
+          <t>...note, when most of these tests were performed, BT had tion (MIC) from ≥4 to 0.5 µg ml−1 for ciprofloxacin and from ≥8 to 1 µg ml−1 already started and test results did not influence patient treatment. for levofloxacin. Of note, patient 91 was treated concomitantly with bac- However, today, on the basis of these results and the overall observa- teriophages and the antibiotics meropenem, colimycin and vancomycin. tion that pathogen eradication is more likely when phages are applied in co...</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>...administration. routine bacterial monitoring generated sufficient suitable samples. We acknowledge that our analysis, involving 100 severely ill This means that the presented bacteriophage resistance data are not patients for whom BT was a salvage therapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blin...</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>...rapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection types were involved. Evaluation of safety failure of eradication was observed in 43%...</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>...ical cultures together with positron emission The phage sourcing process, including phage isolation, charac- tomography/magnetic resonance imaging negative for infec- terization, and full genome sequence, in addition to tion. Remission was defined as the absence of clinical signs of 2 • OFID • Onallah et al Downloaded from academic.oup.com/ofid/article/10/5/ofad221/7133195 by guest on 20 August 2026A B C Figure 1. A, Phage request registry and processing workflow at the Israeli Phage Therapy Cente...</t>
+          <t>...e responsibility of, Bacteriophage activity, increasing bacterial killing when used in combination with Therapy Providers in several hospitals in Belgium and abroad. No these antibiotics, and potentially decreasing selection of antibiotic- blinding, masking or randomization were implemented, and inves- or bacteriophage-resistant clones. However, caution is warranted, as tigators and patients were aware of the bacteriophage treatment. certain antibiotics can interfere with bacteriopha...</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>...hage sons (GraphPad v.0.5.1) was used for G. mellonella survival curve product and clinical data were recorded in a Research Electronic Data comparisons. Capture (REDCap) designed database88. Data collection and analysis were not performed blind to the conditions of the experiments. Reporting summary Further information on research design is available in the Nature Definitions Portfolio Reporting Summary linked to this article. In accordance with the guidelines of an international...</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3481,17 +3495,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3501,24 +3515,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>...TC is currently the leading therapy for patients and their specific bacterial infections [8–14]. and only center in Israel focusing on phage therapy. It provides all services related to phage therapy—phage discovery and charac- terization, phage susceptibility and matching tests, authorization of Received 05 January 2023; editorial decision 17 April 2023; accepted 19 April 2023; pub- lished online 20 April 2023 treatments for patients from Israel and abroad, and delivering and aMembers of the IP...</t>
+          <t>...ct PRJNA975428. All other data supporting the findings of infection persisted for more than 6 months, it was considered a ‘chronic this study are available within the paper. Readers can apply for access infection’. Clinical improvement was defined as the improvement of at to data, which will be supplied in compliance with the obligations and least one symptom associated with the bacterial infection, as assessed responsibilities that the investigators hold for the patients involved in by the treating p...</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3528,471 +3542,483 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>...at The Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing framework previously published by the group [23, 24]. In all Israeli centers, clinical microbiology laboratories follow Phage susceptibility testing was performed in several steps, pathogen identification using matrix-assisted laser desorp- using at least 3 methods [24]. First, a spot assay screen, using tion/ionization–time of flight (MALDI-TOF) and the Vitek all relevant phag...</t>
+          <t>...cs were applied (for example, the study. Source data are provided with this paper. illness severity scores). The influence of other (medical/surgical) inter- ventions was not determined. Eradication of the targeted bacterium was References defined as the absence of the originally targeted causative agent of the 1. Antimicrobial Resistance Collaborators. Global burden of bacterial infection in culture, or when the patient’s treating physician bacterial antimicrobial resistance in 2019: a systematic...</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>...hages in our phage bank, was performed [23]. system. All the strains (Israeli and abroad) that were submitted Phages that yielded clear plaques in this assay were picked for have undergone identification and sensitivity testing according a plaque-forming unit count. The third step was kinetic deter- to the routine clinical microbiology laboratory at the Hadassah mination of the efficacy of the phages with and without the rel- Medical Center. Pathogen identification of all isolates was car-...</t>
+          <t>...to be linked to BT. While our analysis is limited by the uncontrolled nature of these data, it indicates that BT can be effective in combination with antibiotics and can inform the design of future controlled clinical trials. BT100 study, ClinicalTrials.gov registration: NCT05498363. e-mail: jean-paul.pirnay@mil.be Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1434Article https://doi.org/10.1038/s41564-024-01705-x Antimicrobial resistance (AMR) is a prominent global health threat wit...</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>...22. The following data were collected: patient Phage Therapy in Israel • OFID • 1 Downloaded from academic.oup.com/ofid/article/10/5/ofad221/7133195 by guest on 20 August 2026demographics, clinical indication, bacterial pathogen, and anti- susceptibility testing and phage-antibiotic kinetic assays, were biotic susceptibility of the pathogen. performed by the Israeli Phage Bank at The Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing fr...</t>
+          <t>...nd protocol (MiSeq v3 chemistry, Illumina). Trim- informed consent. There was no patient compensation for participa- ming of short reads was performed with Trimmomatic (v.0.32)59. In tion in this study. The observational study protocol was registered on addition, for bacterial production strains, long-read sequencing was ClinicalTrials.gov (Study BT100, ID: NCT05498363). performed using Oxford Nanopore Technologies (ONT)’s rapid bar- coding kit SQK-RBK004 and a MinION flow cell (v.9.4.1),...</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>...Hebrew University of Jerusalem (Hazan Laboratory) according to a Microbial Identification and Resistance Testing framework previously published by the group [23, 24]. In all Israeli centers, clinical microbiology laboratories follow Phage susceptibility testing was performed in several steps, pathogen identification using matrix-assisted laser desorp- using at least 3 methods [24]. First, a spot assay screen, using tion/ionization–time of flight (MALDI-TOF) and the Vitek all relevant phages in ou...</t>
+          <t>...for the resistance (XDR) as non-susceptibility to at least one agent in all but retrospective, observational study is available at https://clinicaltrials. two or fewer antimicrobial categories, and pandrug resistance (PDR) as gov/ct2/show/NCT05498363?term=NCT05498363&amp;draw=2&amp;rank=1. non-susceptibility to all agents in all antimicrobial categories89. The term The bacteriophage genome sequences can be retrieved in the GenBank ‘usual drug resistance’ (UDR) was used to describe isolates tha...</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>...s was car- evant antibiotics. This step reveals also possible antagonistic or ried out using a MALDI-TOF mass spectrometer (bioMérieux, synergistic effects of phages and antibiotics. When the optical Marcy l’Etoile, France), and antibiotic susceptibility testing was density in this assay is below the detection threshold, due to ly- conducted utilizing the VITEK 2 system (bioMérieux) follow- sis, a colony-forming unit count was also performed to detect if ing the Clinical and Laboratory Standards I...</t>
+          <t>...dentified BT database contain- tion pertaining to the analysed patient population. ing demographic, bacteriophage product and clinical data showed Nevertheless, the knowledge gained from these cases is likely to that personalized BT of 100 consecutive patients targeted 114 help physicians to select effective treatment protocols and design difficult-to-treat infections (as diagnosed by the treating physicians), future clinical trials. including 14 second-site infections. Baseline characteristics...</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>...age requests and served as a clinical research file Astrid Military Hospital, Brussels, Belgium). for phage therapy cases (see Supplementary Form). Study data were collected and managed using REDCap electronic Patient Consent Statement and Ethics Approvals data capture tools hosted at the Hadassah Medical Center. For each patient, informed consent was obtained. Additionally, according to the regulations in Israel for each individual treat- Communication ment, a formal approval of the local...</t>
+          <t>...(ABCONCOM) were not selected the first dose43. The ARLG Phage Taskforce, however, acknowledges that in the overall logistic regression model. This could be attributed to clinical outcomes are not always improved with higher doses, reflect- confounding relations between these three variables within this data- ing the complexity of effective bacteriophage dosing. We observed an set. A significant association was found between clinical improvement increase in in vitro bacteriophage efficie...</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>...s data capture tools hosted at the Hadassah Medical Center. For each patient, informed consent was obtained. Additionally, according to the regulations in Israel for each individual treat- Communication ment, a formal approval of the local institutional review board Requests were sent mostly by physicians from different hospi- (IRB/ethics committee) and the Ministry of Health was neces- tals and health centers in Israel (91% of all requests), with 9% of sary for initiating compassionate therapy,...</t>
+          <t>...e presented bacteriophage resistance data are not patients for whom BT was a salvage therapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection ty...</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>...and the Ministry of Health was neces- tals and health centers in Israel (91% of all requests), with 9% of sary for initiating compassionate therapy, together with obtain- requests coming from abroad. All requests were sent initially to ing informed consent from each patient. Publication was done an infectious diseases specialist (R. N.-P.) at the Hadassah- upon the following Hadassah IRB approval numbers: 0420-12- Hebrew University Medical Center and then relayed to the lab- HMO, 0309-18-HMO...</t>
+          <t>...performed a regression analysis to identify functional relationships. The most common indications were lower respiratory tract, skin and soft tissue, and bone infections, and involved combinations of 26 bacteriophages and 6 defined bacteriophage cocktails, individually selected and sometimes pre-adapted to target the causative bacterial pathogens. Clinical improvement and eradication of the targeted bacteria were reported for 77.2% and 61.3% of infections, respectively. In our dataset of 1...</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>...withUTI[4]. ArecentlypublishedreviewonPTinUTIsummarized withregardtojurisdictionalclaimsin currentlyavailabledatasuggestingthatthismodeoftreatmentmaybeanattractiveoption publishedmapsandinstitutionalaffil- forthosepatients[5].Nevertheless,arandomized,placebo-controlled,double-blindclinical iations. trialofintravesicalPTfortreatingUTIinpatientsundergoingtransurethralresectionof theprostatewasnotfoundtobesuperiortoplacebobladderirrigation[6]. Therefore,new studiesandmoredataareneededtocl...</t>
+          <t>...o target the causative bacterial pathogens. Clinical improvement and eradication of the targeted bacteria were reported for 77.2% and 61.3% of infections, respectively. In our dataset of 100 cases, eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749). In vivo selection of bacteriophage resistance and in vitro bacteriophage–antibiotic synergy were documented in 43.8% (7/16 patients) and 90% (9/10) of evaluated patients...</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>...PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provided conclusive data confirming the real therapeutic valueofthetherapy. Therefore,thereisanurgentneedforawell-plannedclinicaltrialthat coulddeterminewhetherindeedPTcanofferareliableweaponagainstantibiotic-resistant b...</t>
+          <t>...5-x Antimicrobial resistance (AMR) is a prominent global health threat with bacteriophages targeting the infecting bacteria (Extended Data Fig. 1). an estimated 1.27 million attributable deaths in 20191 and there is an Personalized bacteriophage preparations were produced at the QAMH urgent need to seek alternative antimicrobial strategies. Bacteriophage in accordance with the rules in force in the territory at the time of their therapy (BT), the use of bacteriophages—the viruses of bacteria—...</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>...li, N.; Goderdzishvili, M.; Chkonia, I.; Rigvava, S.; Chkhotua, A.; Changashvili, G.; McCallin, S.; Schneider, M.P.; etal. Intravesicalbacteriophagesfortreatingurinarytractinfectionsinpatientsundergoing transurethralresectionoftheprostate:Arandomised,placebo-controlled,double-blindclinicaltrial.LancetInfect.Dis.2021,21, 427–436.[CrossRef] 7. Mie˛dzybrodzki,R.;Borysowski,J.;Weber-Da˛browska,B.;Fortuna,W.;Letkiewicz,S.;Szufnarowski,K.;Pawełczyk,Z.;Rogóz˙,P.; Kłak,M.;Wojtasik,E.;etal.Clin...</t>
+          <t>...preparations; the quartiles to the last data point within 1.5 × the interquartile range. Data points DH, article 37 (unproven interventions in clinical practice) of the Declaration plotted outside the boundary of the whiskers are outliers. Female patients are of Helsinki; SOC UM, standard-of-care with unlicensed medicines; ATU MP, represented by purple filled circles and male patients by blue filled circles. ‘Autorisation Temporaire d’Utilisation’ of magistral preparations. c, Primary e, T...</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>...its successful use in treating multidrug-resistantbacterialinfectionsarepublishedalmosteverymonth[9–17]. Like- wise, several reviews on PT are published each year. However, there is a growing gap between the expansion of PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provid...</t>
+          <t>...the basis of OD 600 measurements and validated using a classical plate culture method. Diagnostic tests in support of bacteriophage therapy Antibiotics and bacteriophages were added at subMIC (0.5 × MIC) levels In addition to bacteriophage susceptibility testing, three BT supportive and MOIs ≤ 1.0 (calculated on the propagation host), respectively. The tests were offered without obligation to the Bacteriophage Therapy titres of the bacteriophages were confirmed after each experiment using Provider...</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>...ArecentlypublishedreviewonPTinUTIsummarized withregardtojurisdictionalclaimsin currentlyavailabledatasuggestingthatthismodeoftreatmentmaybeanattractiveoption publishedmapsandinstitutionalaffil- forthosepatients[5].Nevertheless,arandomized,placebo-controlled,double-blindclinical iations. trialofintravesicalPTfortreatingUTIinpatientsundergoingtransurethralresectionof theprostatewasnotfoundtobesuperiortoplacebobladderirrigation[6]. Therefore,new studiesandmoredataareneededtoclarifythevalueofPTin...</t>
+          <t>...g resistant strains. 129 (2017). Front. Microbiol. 12, 783722 (2021). 16. Lebeaux, D. et al. A case of phage therapy against 36. Yoshida, H., Bogaki, M., Nakamura, M. &amp; Nakamura, S. Quinolone pandrug-resistant Achromobacter xylosoxidans in a 12-year-old resistance-determining region in the DNA gyrase gyrA gene lung-transplanted cystic fibrosis patient. Viruses 13, 60 (2021). of Escherichia coli. Antimicrob. Agents Chemother. 34, 1271–1272 17. Van Nieuwenhuyse, B. et al. Bacteriophage-anti...</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>...s a growing gap between the expansion of PT carried out as compassionate use (experimental therapy) andthelackofreliabledataderivedfromclinicaltrialsofPTperformedaccordingtothe requiredstandardsofEvidence-BasedMedicineandEMA(FDA).Notably,nodouble-blindAntibiotics2021,10,627 8of9 randomized clinical trial has provided conclusive data confirming the real therapeutic valueofthetherapy. Therefore,thereisanurgentneedforawell-plannedclinicaltrialthat coulddeterminewhetherindeedPTcanofferarelia...</t>
+          <t>...cation47. of suspected adverse drug reactions and events were assessed by the A considerable body of experimental data has accumulated show- treating physicians. ing that bacteriophages can substantially affect immune system cells, Written informed consent for BT was obtained from the involved and it has been assumed that anti-bacteriophage antibodies appearing patients or their legal representatives according to local provisions. Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1445Ar...</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>...erdzishvili, M.; Chkonia, I.; Rigvava, S.; Chkhotua, A.; Changashvili, G.; McCallin, S.; Schneider, M.P.; etal. Intravesicalbacteriophagesfortreatingurinarytractinfectionsinpatientsundergoing transurethralresectionoftheprostate:Arandomised,placebo-controlled,double-blindclinicaltrial.LancetInfect.Dis.2021,21, 427–436.[CrossRef] 7. Mie˛dzybrodzki,R.;Borysowski,J.;Weber-Da˛browska,B.;Fortuna,W.;Letkiewicz,S.;Szufnarowski,K.;Pawełczyk,Z.;Rogóz˙,P.; Kłak,M.;Wojtasik,E.;etal.Clinicalaspectsofphaget...</t>
+          <t>...-bacteriophage antibodies appearing patients or their legal representatives according to local provisions. Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1445Article https://doi.org/10.1038/s41564-024-01705-x Where warranted, local ethics committee approval for BT was obtained. safety of the bacteriophage to be used in human therapy. For this According to EU Regulation No 536/2014 (Clinical Trials Regulation)57, purpose, genomic DNA of the bacteriophages and their bacterial its trans...</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>...dentified BT database was not considered as aration kit and sequenced on an Illumina MiSeq instrument with a an experiment on the human person and did not require a dedicated 250 bp paired-end protocol (MiSeq v3 chemistry, Illumina). Trim- informed consent. There was no patient compensation for participa- ming of short reads was performed with Trimmomatic (v.0.32)59. In tion in this study. The observational study protocol was registered on addition, for bacterial production strains, long-rea...</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>...ld have been partly due to an inability to provide the necessary information. For instance, access to medical data could have been hampered by a lack of confidence from the treating physicians. Thiscouldhavebeenpartiallyremediedbyconductingrandomizedcontrolledtrialstodemonstrate phage therapy efficacy and by awareness campaigns. The QAMH is developing tools, such asViruses2019,11,265 9of11 acomprehensivewebsitewithinformationandinstructions,todispensephagetherapyinformationto healthcar...</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>...ust keep in mind that phages are not “miracle drugs”, as antibiotics were once presented, but that they are probably only useful as additional tools in certain indications and conditions,whichstillneedtobedetermined. Assuch,morephagetherapyrandomizedcontrolled trialsareneeded,andphageantibioticsynergy(PAS)shouldbefurtherexplored[18,19]. Withthisreport,wehopetohelpandguidethe“phagetherapycentersinthemaking”,whichare slowlyemergingfromthe“phage-averse”settingcalledWesternmedicine. Supple...</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4005,98 +4031,86 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>...ed monovalent lysates of bacteriophagepreparationsofEscherichiacoli, Klebsiellapneumoniae, Enterococcusfaecalis or Pseudomonas aeruginosa based on phage typing (Tables 1 and 2). Phage lysates had concentrationsof106–108plaqueformingunit/mL(pfu/mL).Healthydonorsdidnotuse bacteriophagepreparations,buttheirserawereexaminedforthepresenceofantiphage antibodies against bacteriophage preparations E. coli phage coli 48/D1, K. pneumoniae phageKl16/30,E.faecalisphageEntc15/PandP.aeruginos...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>...ingphagetherapyandcontrolofhealthyindivid- ualswastestedwiththeplatephageneutralizationtest. TheAASresearchwasperformed accordingtothemethoddescribedearlier[8]. Undilutedanddilutedserafrom1:10to 1:1500weretested. Atotalof50µLofthephagewithatiterof1×106pfu/mLwereadded toeachserumdilution(450µL).Phagetitercontrolwasperformedbyadding50µLofthe phagewithatiterof1×106 pfu/mLto450µLofbroth. Themixturewasincubatedfor 30minat37◦C.Afterthistime,50µLofthemixtureweretakenandaddedto4.95mL ofco...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>...ereadded toeachserumdilution(450µL).Phagetitercontrolwasperformedbyadding50µLofthe phagewithatiterof1×106 pfu/mLto450µLofbroth. Themixturewasincubatedfor 30minat37◦C.Afterthistime,50µLofthemixtureweretakenandaddedto4.95mL ofcoldbroth. Phagetiterwasexaminedatthebeginningofthephagereactionwiththe serumand,afterthe30minreaction,bythestandarddouble-agarlayermethod. Atotal of100µLofthemixtureand200µLofthebacterialstrainwereaddedto3mLof0.7% agarandpouredontoagarplates. Theplateswereincu...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4109,44 +4123,40 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>...erimentsandanalyzeddata;R.M.analyzed data;M.Z˙.designedandperformedtheexperimentsandanalyzeddata;B.W.-D.wrotepartsofthe manuscript;A.G.conceivedthestudyandwrotethemanuscript.Allauthorshavereadandagreed tothepublishedversionofthemanuscript. Funding:Thisresearchreceivednoexternalfunding. InstitutionalReviewBoardStatement:Thestudywasconductedaccordingtotheguidelinesofthe DeclarationofHelsinki,andapprovedbytheBioethicsCommitteeattheWroclawMedicalUniversity (protocoltitle“Phageinactivati...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4156,24 +4166,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>...2023 A list of authors and their affiliations appears at the end of the paper Accepted: 19 April 2024 Published online: 4 June 2024 In contrast to the many reports of successful real-world cases of personalized bacteriophage therapy (BT), randomized controlled Check for updates trials of non-personalized bacteriophage products have not produced the expected results. Here we present the outcomes of a retrospective observational analysis of the first 100 consecutive cases of personalize...</t>
+          <t>...to evaluate its safety and efficacy. In all cases, newinformationmustberecordedand,whereappropriate,madepubliclyavailable. Sincethen,patientshavebeenoccasionallytreatedbyphagetherapyattheQAMH.Lastyear, wereportedthecaseofapatienttreatedwithintravenousbacteriophagemonotherapy(noantibiotics wereused)againstcolistin-only-sensitiveP.aeruginosa[8]. Belgiumisnowimplementingapragmatic phagetherapyframeworkthatcentersonthemagistralpreparation(compoundingpharmaciesinthe US)oftailor-madephagemedi...</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4183,24 +4193,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>...each bacteriophage API batch. The BT protocols that were suggested turing practices (GMP) certification, preclinical research (toxicity and to the treating physicians were based on the experiences of the George pharmacology) and conducting randomized controlled trials (RCTs). Eliava Institute of Bacteriophages, Microbiology and Virology (Eliava However, the handful of bacteriophage RCTs that have been performed Institute) in Tbilisi, Georgia (personal communications), and on the so far...</t>
+          <t>...blications(groupedaccordingtomedicalindicationsandauthoredbythe differenttreatingphysicians)andwillnotbediscussedinthisarticle. However,wecandisclosethat no serious adverse events were observed and that, in general, phage therapy seemed helpful in a considerablenumberofthecases. Wealsowouldliketostressthat,withtheexceptionofonecasethat wasrecentlypublished[8],otherantimicrobialagents(e.g.,antibiotics)wereappliedsimultaneously withthephages. 5. ImplicationsforFutureActivities Mos...</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4210,24 +4220,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>...primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection types were involved. Evaluation of safety failure of eradication was observed in 43% (3/7) of patients...</t>
+          <t>...iol.Infect.2012,18,268–281.[CrossRef][PubMed] 14. Merabishvili,M.;Pirnay,J.P.;Verbeken,G.;Chanishvili,N.;Tediashvili,M.;Lashkhi,N.;Glonti,T.;Krylov,V.; Mast,J.;VanParys,L.;etal. Quality-controlledsmall-scaleproductionofawell-definedbacteriophage cocktailforuseinhumanclinicaltrials.PLoSONE2009,4,e4944.[CrossRef][PubMed] 15. Merabishvili, M.; Vandenheuvel, D.; Kropinski, A.M.; Mast, J.; De Vos, D.; Verbeken, G.; Noben, J.P.; Lavigne,R.;Vaneechoutte,M.;Pirnay,J.P.Characterizationofnewlyisolat...</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4237,253 +4247,241 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>...me of their therapy (BT), the use of bacteriophages—the viruses of bacteria—to use in clinical practice. Of note, most selected cases concerned per- treat bacterial infections, was first applied by Félix d’Hérelle in 19192, sonalized BT as salvage therapy after standard antibiotic treatments and further developed and applied in the former Soviet Union. had failed. Quality and safety of the bacteriophage preparations were A recent systematic review confirmed that BT can generally be verified...</t>
+          <t>...tionassociatedwithantibiotictreatmentfailure; • Theabsenceofothertherapeuticoptions. Wheneligibilitycriteriaweremet,whichwasthecaseforonly20patients(Figure1),aconsultation with an infectious disease specialist was scheduled, during which a physical examination andViruses2019,11,265 8of11 ananamnesisofthepatientwereperformedandbacterialsamplesoftheinfectionsite(s)weretaken. Consecutively, these bacterial samples were sent to the clinical laboratory for standard bacterial culture, isolation, and i...</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>...note, when most of these tests were performed, BT had tion (MIC) from ≥4 to 0.5 µg ml−1 for ciprofloxacin and from ≥8 to 1 µg ml−1 already started and test results did not influence patient treatment. for levofloxacin. Of note, patient 91 was treated concomitantly with bac- However, today, on the basis of these results and the overall observa- teriophages and the antibiotics meropenem, colimycin and vancomycin. tion that pathogen eradication is more likely when phages are applied in co...</t>
+          <t>...;datacuration,S.D.,C.M.,M.M.,P.D.L.;writing–originaldraftpreparation,S.D.andJ.-P.P.;writing–review andediting,S.D.,D.D.V.,M.M.,P.S.andJ.-P.P.;visualization,B.D.andJ.-P.P.;supervision,S.D.,P.S.andJ.-P.P.; projectadministration,P.D.L.andC.M.;fundingacquisition,P.S.andJ.-P.P. Funding:M.M.wassupportedbygrantHFM15-5oftheRoyalHigherInstituteforDefence.Viruses2019,11,265 10of11 Acknowledgments:Theauthorsexpresstheirthankstothepersonneloftheclinicallaboratoryandtothehospital staffandpatient...</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>...administration. routine bacterial monitoring generated sufficient suitable samples. We acknowledge that our analysis, involving 100 severely ill This means that the presented bacteriophage resistance data are not patients for whom BT was a salvage therapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blin...</t>
+          <t>...ria for Which New Antibiotics Are Urgently Needed. Available online:https://www.who.int/news-room/detail/27-02-2017-who-publishes-list-of-bacteria-for-which- new-antibiotics-are-urgently-needed(accessedon10February2019). 4. Rice,L.B.Federalfundingforthestudyofantimicrobialresistanceinnosocomialpathogens:noESKAPE.J. Infect.Dis.2009,197,1079–1081.[CrossRef][PubMed] 5. Boucher,H.W.;Talbot,G.H.;Bradley,J.S.;Edwards,J.E.;Gilbert,D.;Rice,L.B.;Scheld,M.;Spellberg,B.; Bartlett,J.Badbugs,nod...</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>...rapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection types were involved. Evaluation of safety failure of eradication was observed in 43%...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>...e responsibility of, Bacteriophage activity, increasing bacterial killing when used in combination with Therapy Providers in several hospitals in Belgium and abroad. No these antibiotics, and potentially decreasing selection of antibiotic- blinding, masking or randomization were implemented, and inves- or bacteriophage-resistant clones. However, caution is warranted, as tigators and patients were aware of the bacteriophage treatment. certain antibiotics can interfere with bacteriopha...</t>
+          <t>...the individual IND (investigational new All clinical isolates were grown from individual colonies in ly- drug) for each patient on a compassionate-use basis. Each pa- sogeny broth (LB) at 37°C. For plaque (phage) isolation from tient case was treated after approval from the local institutional environmental samples or TAILΦR’s library of phages, a review board (IRB). All patients provided informed consent for double-agar overlay assay was performed using the patient’s clinical use of p...</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>...hage sons (GraphPad v.0.5.1) was used for G. mellonella survival curve product and clinical data were recorded in a Research Electronic Data comparisons. Capture (REDCap) designed database88. Data collection and analysis were not performed blind to the conditions of the experiments. Reporting summary Further information on research design is available in the Nature Definitions Portfolio Reporting Summary linked to this article. In accordance with the guidelines of an international...</t>
+          <t>...ted but 4 weeks lat- noted, but mostly at low concentrations of antibiotic and was er the patient developed an infection caused by Peptoniphilus less apparent in the earlier time point. The physician was in- asaccharolyticus. This patient was treated with an antibiotic formed of this and decided to use ceftriaxone. and avoided hip disarticulation. For case 8 (LVAD; S. aureus), there were no complications; the patient cleared the initial bac- Clinical Outcomes terial infection without d...</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>...: Phage targeted cloacae 692, Enterobacter cloacae (SLC4). IV, 6 wk effects pathogen was eradicated. However, 693, Treatment: phage cocktail and later developed new infection due to 694 cefepime Peptoniphilus asaccharolyticus. The patient was treated successfully with oral amoxicillin-clavulanate and will remain on life-long suppression. E. cloacae was not recovered from any of the cultures at the time of recurrence. The treating physician believed the E. cloacae has been eradicated. A...</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>...ct PRJNA975428. All other data supporting the findings of infection persisted for more than 6 months, it was considered a ‘chronic this study are available within the paper. Readers can apply for access infection’. Clinical improvement was defined as the improvement of at to data, which will be supplied in compliance with the obligations and least one symptom associated with the bacterial infection, as assessed responsibilities that the investigators hold for the patients involved in by the treating p...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>...cs were applied (for example, the study. Source data are provided with this paper. illness severity scores). The influence of other (medical/surgical) inter- ventions was not determined. Eradication of the targeted bacterium was References defined as the absence of the originally targeted causative agent of the 1. Antimicrobial Resistance Collaborators. Global burden of bacterial infection in culture, or when the patient’s treating physician bacterial antimicrobial resistance in 2019: a systematic...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>...to be linked to BT. While our analysis is limited by the uncontrolled nature of these data, it indicates that BT can be effective in combination with antibiotics and can inform the design of future controlled clinical trials. BT100 study, ClinicalTrials.gov registration: NCT05498363. e-mail: jean-paul.pirnay@mil.be Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1434Article https://doi.org/10.1038/s41564-024-01705-x Antimicrobial resistance (AMR) is a prominent global health threat wit...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4498,56 +4496,52 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>...nd protocol (MiSeq v3 chemistry, Illumina). Trim- informed consent. There was no patient compensation for participa- ming of short reads was performed with Trimmomatic (v.0.32)59. In tion in this study. The observational study protocol was registered on addition, for bacterial production strains, long-read sequencing was ClinicalTrials.gov (Study BT100, ID: NCT05498363). performed using Oxford Nanopore Technologies (ONT)’s rapid bar- coding kit SQK-RBK004 and a MinION flow cell (v.9.4.1),...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>...for the resistance (XDR) as non-susceptibility to at least one agent in all but retrospective, observational study is available at https://clinicaltrials. two or fewer antimicrobial categories, and pandrug resistance (PDR) as gov/ct2/show/NCT05498363?term=NCT05498363&amp;draw=2&amp;rank=1. non-susceptibility to all agents in all antimicrobial categories89. The term The bacteriophage genome sequences can be retrieved in the GenBank ‘usual drug resistance’ (UDR) was used to describe isolates tha...</t>
+          <t>...acterials and Innovative Laboratories for Phage (Φ) Research; TEM, Transmission Electron Microscopy; Sub., Submission; Quant., Quantificaiton. The figure was created with BioRender.com. 1080 • CID 2023:77 (15 October) • Green et alTable 1. Inclusion Criteria for Phage Therapy Table 2. Cocktail Report Contents Antibiotic treatment has been ineffective Name and description of phages Multidrug-resistant organism (or difficult-to-treat infection) Manufacturer Chronically infected patienta Descript...</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4557,24 +4551,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>...dentified BT database contain- tion pertaining to the analysed patient population. ing demographic, bacteriophage product and clinical data showed Nevertheless, the knowledge gained from these cases is likely to that personalized BT of 100 consecutive patients targeted 114 help physicians to select effective treatment protocols and design difficult-to-treat infections (as diagnosed by the treating physicians), future clinical trials. including 14 second-site infections. Baseline characteristics...</t>
+          <t>...as by our group but was based on a clinical profile provided by we improved efficiency over time (Supplementary Figure 1). the treating physicians. Of the 12 patient cases, more than 50% (7/12 cases) had a secondary immune deficiency. Ten Phage Cocktails Were Generated Against 6 Different Species TAILΦR had originally provided phages for 12 patients. For 1 case, we were not provided sufficient clinical information despite Mode of Administration treatment being regarded as successful, so w...</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4584,24 +4578,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>...(ABCONCOM) were not selected the first dose43. The ARLG Phage Taskforce, however, acknowledges that in the overall logistic regression model. This could be attributed to clinical outcomes are not always improved with higher doses, reflect- confounding relations between these three variables within this data- ing the complexity of effective bacteriophage dosing. We observed an set. A significant association was found between clinical improvement increase in in vitro bacteriophage efficie...</t>
+          <t>...s TAILΦR had originally provided phages for 12 patients. For 1 case, we were not provided sufficient clinical information despite Mode of Administration treatment being regarded as successful, so we omitted this case. All patients received concomitant antibiotic therapy. All pa- One patient was retreated with a different phage cocktail after de- tients were treated with intravenous (IV) phage therapy veloping a new infection (thus, 12 cases) (Tables 5and 6). The (Table 5). Four patient cases (33%)...</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CONFUSION</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4611,24 +4605,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>...e presented bacteriophage resistance data are not patients for whom BT was a salvage therapy and our primary aim was generalizable. In addition, due to the limited number of patients in to help these patients, has intrinsic limitations. No control groups, which resistance was demonstrated, it was not possible to statistically blinding or randomization were put in place and different medical show its potential impact on bacterial target eradication. Regardless, specialties and infection ty...</t>
+          <t>...ed concomitant intraoper- ing data, genomic analysis, and predicted lifestyle of each phage. ative phages. The fourth patient (case 12) received phages top- Based on a sequence analysis, all phages lacked known bacterial ically. All non-IV doses were single one-time applications. The virulence factors (eg, toxins) and antibiotic-resistance genes. average duration for IV treatment was 5.6 weeks. Two different methods were used to assess whether the phage ex- isted as temperate (in...</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4638,363 +4632,347 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>...performed a regression analysis to identify functional relationships. The most common indications were lower respiratory tract, skin and soft tissue, and bone infections, and involved combinations of 26 bacteriophages and 6 defined bacteriophage cocktails, individually selected and sometimes pre-adapted to target the causative bacterial pathogens. Clinical improvement and eradication of the targeted bacteria were reported for 77.2% and 61.3% of infections, respectively. In our dataset of 1...</t>
+          <t>...ts with CF with lung infection. Terwilliger et al., 2022) and 12 (Figure 3). Of particular note is case 8 in which 2 antibiotics were tested (Figure 1Hi, Hii): ceftriaxone and cefazolin. For the phage cocktail with cefazolin, likely due to comorbidities of the patients. For example, in we observed antagonism. For ceftriaxone, antagonism was also case 2 (PJI; E. cloacae), E. cloacae was eradicated but 4 weeks lat- noted, but mostly at low concentrations of antibiotic and was er the pati...</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>...o target the causative bacterial pathogens. Clinical improvement and eradication of the targeted bacteria were reported for 77.2% and 61.3% of infections, respectively. In our dataset of 100 cases, eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749). In vivo selection of bacteriophage resistance and in vitro bacteriophage–antibiotic synergy were documented in 43.8% (7/16 patients) and 90% (9/10) of evaluated patients...</t>
+          <t>...asis. Each pa- sogeny broth (LB) at 37°C. For plaque (phage) isolation from tient case was treated after approval from the local institutional environmental samples or TAILΦR’s library of phages, a review board (IRB). All patients provided informed consent for double-agar overlay assay was performed using the patient’s clinical use of phages and their data being used for research bacterial isolate as host. Individual plaques were serially pas- purposes and publication. The manufacturing inst...</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>...5-x Antimicrobial resistance (AMR) is a prominent global health threat with bacteriophages targeting the infecting bacteria (Extended Data Fig. 1). an estimated 1.27 million attributable deaths in 20191 and there is an Personalized bacteriophage preparations were produced at the QAMH urgent need to seek alternative antimicrobial strategies. Bacteriophage in accordance with the rules in force in the territory at the time of their therapy (BT), the use of bacteriophages—the viruses of bacteria—...</t>
+          <t>...A. A. F. and K. L. W. provided phages for treat- All other authors report no potential conflicts. All authors have submit- ment and reviewed and edited the manuscript. A. L. T. organized phage ted the ICMJE Form for Disclosure of Potential Conflicts of Interest. therapy treatments; contributed to data collection, analysis, and interpreta- Conflicts that the editors consider relevant to the content of the manuscript tion; and reviewed and edited the manuscript. B. W. T. provided necessary have bee...</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>...preparations; the quartiles to the last data point within 1.5 × the interquartile range. Data points DH, article 37 (unproven interventions in clinical practice) of the Declaration plotted outside the boundary of the whiskers are outliers. Female patients are of Helsinki; SOC UM, standard-of-care with unlicensed medicines; ATU MP, represented by purple filled circles and male patients by blue filled circles. ‘Autorisation Temporaire d’Utilisation’ of magistral preparations. c, Primary e, T...</t>
+          <t>...atments; contributed to data collection, analysis, and interpreta- Conflicts that the editors consider relevant to the content of the manuscript tion; and reviewed and edited the manuscript. B. W. T. provided necessary have been disclosed. funding for the work at TAILOR and reviewed and provided edits for the manuscript. A. M. is the faculty founder and current Center Director of References TAILOR, analyzed and interpretated data, and wrote and edited the 1. World Health Organizatio...</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>ALEATORIZACION</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>...the basis of OD 600 measurements and validated using a classical plate culture method. Diagnostic tests in support of bacteriophage therapy Antibiotics and bacteriophages were added at subMIC (0.5 × MIC) levels In addition to bacteriophage susceptibility testing, three BT supportive and MOIs ≤ 1.0 (calculated on the propagation host), respectively. The tests were offered without obligation to the Bacteriophage Therapy titres of the bacteriophages were confirmed after each experiment using Provider...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>...g resistant strains. 129 (2017). Front. Microbiol. 12, 783722 (2021). 16. Lebeaux, D. et al. A case of phage therapy against 36. Yoshida, H., Bogaki, M., Nakamura, M. &amp; Nakamura, S. Quinolone pandrug-resistant Achromobacter xylosoxidans in a 12-year-old resistance-determining region in the DNA gyrase gyrA gene lung-transplanted cystic fibrosis patient. Viruses 13, 60 (2021). of Escherichia coli. Antimicrob. Agents Chemother. 34, 1271–1272 17. Van Nieuwenhuyse, B. et al. Bacteriophage-anti...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>CEGAMIENTO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>...cation47. of suspected adverse drug reactions and events were assessed by the A considerable body of experimental data has accumulated show- treating physicians. ing that bacteriophages can substantially affect immune system cells, Written informed consent for BT was obtained from the involved and it has been assumed that anti-bacteriophage antibodies appearing patients or their legal representatives according to local provisions. Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1445Ar...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>...-bacteriophage antibodies appearing patients or their legal representatives according to local provisions. Nature Microbiology | Volume 9 | June 2024 | 1434–1453 1445Article https://doi.org/10.1038/s41564-024-01705-x Where warranted, local ethics committee approval for BT was obtained. safety of the bacteriophage to be used in human therapy. For this According to EU Regulation No 536/2014 (Clinical Trials Regulation)57, purpose, genomic DNA of the bacteriophages and their bacterial its trans...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Medición del desenlace (RoB 2, dominio 4)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>...dentified BT database was not considered as aration kit and sequenced on an Illumina MiSeq instrument with a an experiment on the human person and did not require a dedicated 250 bp paired-end protocol (MiSeq v3 chemistry, Illumina). Trim- informed consent. There was no patient compensation for participa- ming of short reads was performed with Trimmomatic (v.0.32)59. In tion in this study. The observational study protocol was registered on addition, for bacterial production strains, long-rea...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>...ld have been partly due to an inability to provide the necessary information. For instance, access to medical data could have been hampered by a lack of confidence from the treating physicians. Thiscouldhavebeenpartiallyremediedbyconductingrandomizedcontrolledtrialstodemonstrate phage therapy efficacy and by awareness campaigns. The QAMH is developing tools, such asViruses2019,11,265 9of11 acomprehensivewebsitewithinformationandinstructions,todispensephagetherapyinformationto healthcar...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>...ust keep in mind that phages are not “miracle drugs”, as antibiotics were once presented, but that they are probably only useful as additional tools in certain indications and conditions,whichstillneedtobedetermined. Assuch,morephagetherapyrandomizedcontrolled trialsareneeded,andphageantibioticsynergy(PAS)shouldbefurtherexplored[18,19]. Withthisreport,wehopetohelpandguidethe“phagetherapycentersinthemaking”,whichare slowlyemergingfromthe“phage-averse”settingcalledWesternmedicine. Supple...</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DESVIACIONES</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>...ious studies have shown that the level of antiphage activity of sera (AAS) calculated as the rate of phage inactivation (K) in patients undergoing PT depends on several factors such as the route of phage administration, phage type, and the dose of the phage preparation (Figure 1) [6]. Oral and rectal administration of phages are considered the least immunogenic, whereas the combination of both local and oral administration is more immunogenic. Purified phage preparations with hig...</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CEGAMIENTO</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>...age preparation (Figure 1) [6]. Oral and rectal administration of phages are considered the least immunogenic, whereas the combination of both local and oral administration is more immunogenic. Purified phage preparations with higher phage titer may be more Antibiotics2025,14,87 immunogenic in comparison to phage lysates [6]. The correlation between the h2igohf1e0r phage titer and the higher antibody level is not a rule, and the degree of phage purification may also play an essent...</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PERDIDAS</t>
+          <t>CLASIFICACION</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
+          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>...is not a rule, and the degree of phage purification may also play an essential part. Żaczek et al. [7] showed that sometimes lysates are more Ourpreviousstudieshaveshownthatthelevelofantiphageactivityofsera(AAS) immunogenic (despite lower titers) than purified preparations, which was explained by calculated as the rate of phage inactivation (K) in patients undergoing PT depends on the influence of impurities on the higher antibody levels. Antibody responses to phage severalfactor...</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MEDICION</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
+          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5007,30 +4985,34 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REPORTE</t>
+          <t>CONFLICTOS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
+          <t>Financiación, conflictos de interés y consentimiento</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>...therapy,R.M.;resources, M.Ł.-S.andA.G.;writing—originaldraftpreparation,M.Ł.-S.,B.W.-D.andA.G.;writing—review&amp; editing,M.Ł.-S.,M.Z˙.andA.G.;supervision,A.G.,M.Ł.-S.andB.W.-D.Allauthorshavereadand agreedtothepublishedversionofthemanuscript. Funding:ThisworkwassupportedbyinstitutionalfundsfromtheHirszfeldInstituteofImmunology andExperimentalTherapyofthePolishAcademyofSciences. InstitutionalReviewBoardStatement: ThestudywasconductedbytheDeclarationofHelsinki, andapprovedbytheBioethicsC...</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5040,30 +5022,34 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
+          <t>Sesgo por confusión</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>"When phage therapy was initiated, all patients were concurrently on IV antibiotics (n = 6) or recently completed antibiotics (n = 3)." || Nota: No hubo asignación comparativa ni ajuste por gravedad basal, tratamientos concomitantes o diferencias clínicas; el efecto de la fagoterapia no puede separarse de cointervenciones ni pronóstico.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>CONFUSION</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Sesgo en la selección de los participantes</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5073,14 +5059,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>...to evaluate its safety and efficacy. In all cases, newinformationmustberecordedand,whereappropriate,madepubliclyavailable. Sincethen,patientshavebeenoccasionallytreatedbyphagetherapyattheQAMH.Lastyear, wereportedthecaseofapatienttreatedwithintravenousbacteriophagemonotherapy(noantibiotics wereused)againstcolistin-only-sensitiveP.aeruginosa[8]. Belgiumisnowimplementingapragmatic phagetherapyframeworkthatcentersonthemagistralpreparation(compoundingpharmaciesinthe US)oftailor-madephagemedi...</t>
+          <t>"Individuals were selected for treatment owing to a combination of the following: lack of clinical response to antibiotics, persistent symptoms and/or clinical decline despite comprehensive CF care, severity of pulmonary exacerbations, and no additional approved therapeutics available." || Nota: Selección clínica por compasión y gravedad; no se describe muestreo consecutivo ni una población fuente comparable. El brazo A es además una serie de casos.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5090,61 +5076,61 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Sesgo en la clasificación de las intervenciones</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>...blications(groupedaccordingtomedicalindicationsandauthoredbythe differenttreatingphysicians)andwillnotbediscussedinthisarticle. However,wecandisclosethat no serious adverse events were observed and that, in general, phage therapy seemed helpful in a considerablenumberofthecases. Wealsowouldliketostressthat,withtheexceptionofonecasethat wasrecentlypublished[8],otherantimicrobialagents(e.g.,antibiotics)wereappliedsimultaneously withthephages. 5. ImplicationsforFutureActivities Mos...</t>
+          <t>"Phage therapy was personalized on the basis of susceptibility of the PsA sputum isolates to phages in the phage library." || Nota: La intervención se define y verifica mediante susceptibilidad del aislado; no obstante, hubo single-phage y cócteles, con dosis/frecuencias y nebulizadores no idénticos.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CLASIFICACION</t>
+          <t>DESVIACIONES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
+          <t>Sesgo por desviaciones de las intervenciones previstas</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>...iol.Infect.2012,18,268–281.[CrossRef][PubMed] 14. Merabishvili,M.;Pirnay,J.P.;Verbeken,G.;Chanishvili,N.;Tediashvili,M.;Lashkhi,N.;Glonti,T.;Krylov,V.; Mast,J.;VanParys,L.;etal. Quality-controlledsmall-scaleproductionofawell-definedbacteriophage cocktailforuseinhumanclinicaltrials.PLoSONE2009,4,e4944.[CrossRef][PubMed] 15. Merabishvili, M.; Vandenheuvel, D.; Kropinski, A.M.; Mast, J.; De Vos, D.; Verbeken, G.; Noben, J.P.; Lavigne,R.;Vaneechoutte,M.;Pirnay,J.P.Characterizationofnewlyisolat...</t>
+          <t>"Across the cohort, there were differences in the number of phages used (for example, single versus cocktail), duration of phage therapy (7-10 days) and frequency of treatment (inpatient and outpatient)." || Nota: La intervención y la administración variaron entre participantes y no existió comparador; las desviaciones y cointervenciones impiden interpretar una comparación interna.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>PERDIDAS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
+          <t>Sesgo por datos faltantes</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5154,24 +5140,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>...tionassociatedwithantibiotictreatmentfailure; • Theabsenceofothertherapeuticoptions. Wheneligibilitycriteriaweremet,whichwasthecaseforonly20patients(Figure1),aconsultation with an infectious disease specialist was scheduled, during which a physical examination andViruses2019,11,265 8of11 ananamnesisofthepatientwereperformedandbacterialsamplesoftheinfectionsite(s)weretaken. Consecutively, these bacterial samples were sent to the clinical laboratory for standard bacterial culture, isolation, and i...</t>
+          <t>"Sputum samples were collected at different intervals over the subsequent 28 days ... and spirometry was performed after phage therapy (21-30 days) at each patient's CF center." || Nota: Los tiempos de recogida variaron; además, el seguimiento de eventos adversos dependió del reporte de pacientes/equipos y no hubo cuestionarios estandarizados ni comité de seguridad.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>MEDICION</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Sesgo en la medición de los desenlaces</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5181,51 +5167,51 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>...;datacuration,S.D.,C.M.,M.M.,P.D.L.;writing–originaldraftpreparation,S.D.andJ.-P.P.;writing–review andediting,S.D.,D.D.V.,M.M.,P.S.andJ.-P.P.;visualization,B.D.andJ.-P.P.;supervision,S.D.,P.S.andJ.-P.P.; projectadministration,P.D.L.andC.M.;fundingacquisition,P.S.andJ.-P.P. Funding:M.M.wassupportedbygrantHFM15-5oftheRoyalHigherInstituteforDefence.Viruses2019,11,265 10of11 Acknowledgments:Theauthorsexpresstheirthankstothepersonneloftheclinicallaboratoryandtothehospital staffandpatient...</t>
+          <t>"Because each case was a SPIND, standardized CF symptom diaries or questionnaires were not used and there was no safety monitoring board." || Nota: No se describe un protocolo prospectivo de resultados ni registro de desenlaces; se presentan varios análisis microbiológicos, clínicos y fenotípicos sin una jerarquía clara de selección del resultado.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CONFLICTOS</t>
+          <t>REPORTE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
+          <t>Sesgo en la selección del resultado notificado</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>...ria for Which New Antibiotics Are Urgently Needed. Available online:https://www.who.int/news-room/detail/27-02-2017-who-publishes-list-of-bacteria-for-which- new-antibiotics-are-urgently-needed(accessedon10February2019). 4. Rice,L.B.Federalfundingforthestudyofantimicrobialresistanceinnosocomialpathogens:noESKAPE.J. Infect.Dis.2009,197,1079–1081.[CrossRef][PubMed] 5. Boucher,H.W.;Talbot,G.H.;Bradley,J.S.;Edwards,J.E.;Gilbert,D.;Rice,L.B.;Scheld,M.;Spellberg,B.; Bartlett,J.Badbugs,nod...</t>
+          <t>"Here, we present outcomes from the first nine adult pwCF compassionate cases who were treated with nebulized phage(s) using the above approach." || Nota: Serie consecutiva de casos compasivos, sin comparador y con múltiples desenlaces; no se identifica un plan de análisis preespecificado que permita descartar selección del resultado reportado.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-004</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ALEATORIZACION</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
+          <t>Juicio global del estudio</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5235,1437 +5221,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>...ORIGINAL ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Therapy: A Randomized Controlled Trial Kavita Meena1 , Rajesh K Meena2 , Sarita Kumari3 , Premkumar Thambidurai4 , Gopal Nath5 Received on: 20 August 2025; Accepted on: 05 January 2026; Published on: 18 March 2026 Visual Abstract Supplement Material AbstrAct Ba...</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>ALEATORIZACION</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>...ntial “alternative.” We aimed to evaluate the efficacy and safety of topical bacteriophage therapy for the management of PUs in critically ill ICU patients and its comparison to conventional therapy. Patients and methods: This prospective, randomized, double-blind controlled trial was conducted in the ICU of a tertiary care center between April 2024 and May 2025. Seventy-six adult patients with grade II–IV PUs were screened, and 68 were enrolled (34 in each group). Group C received con...</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>ALEATORIZACION</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>...K, Meena RK, Kumari S, Thambidurai in critically ill trauma patients. P, Nath G. Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison introduction to Conventional Therapy: A Randomized Controlled Trial. Indian J Crit Care Med 2026;30(3):196–203. Trauma is a modern-day epidemic, with a marked increase in the Source of support: Nil number of accidents due to the rapid growth of the motor industry Conflict of interest: None...</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>...OI: 10.1007/978-1-4939-7395-8_13. 4. Ross P, Du Plooy D, Sheldrake J, Ronayne L, Keogh P, Collins K, et al. 22. Fish R, Kutter E, Wheat G, Blasdel B, Kutateladze M, Kuhl S. The epidemiology of pressure injuries in adult intensive care unit Compassionate use of bacteriophage therapy for foot ulcer treatment 202 Indian Journal of Critical Care Medicine, Volume 30 Issue 3 (March 2026)Bacteriophage Therapy in Pressure Ulcers as an effective step for moving toward clinical trials. Methods Mol 27....</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>CEGAMIENTO</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>...native.” We aimed to evaluate the efficacy and safety of topical bacteriophage therapy for the management of PUs in critically ill ICU patients and its comparison to conventional therapy. Patients and methods: This prospective, randomized, double-blind controlled trial was conducted in the ICU of a tertiary care center between April 2024 and May 2025. Seventy-six adult patients with grade II–IV PUs were screened, and 68 were enrolled (34 in each group). Group C received conventional ther...</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>CEGAMIENTO</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>...patient was observed for local adverse reactions (such as erythema, warmth, PAtients And MetHods increased discharge, hypersensitivity, or ulcer deterioration) and systemic adverse events in the bacteriophage group. This was a prospective, double blind, randomized study that was conducted in the ICU of an apex care center in the Department Sample Size of Anaesthesiology and Microbiology. The study period was Based on the previous study, “Biological therapy on infected from April 2024 to...</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>CEGAMIENTO</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>...Ulcers 30 28 25 25 24 24 20 18 18 18 17 15 15 15 15 15 14 14 13 10 5 0 on phage therapy have focused mainly on chronic wounds or ambulatory patients, such as those with diabetic foot ulcers, venous leg ulcers, and burn wounds. A randomized double-blind trial by Karn et al. reported wound sterilization in 93.3% of cases and complete healing by day 90 with personalized phage therapy, showing its clinical potential.8 A systematic review by Narayanan et al. highlighted the potential of phage...</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>PERDIDAS</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>...gibility (n = 76) Excluded (n = 0) Enrolled for study (n = 76) Allocated to intervention (n = 38) Allocated to intervention (n = 38) Conventional pressure ulcer Conventional pressure ulcer therapy therapy plus topical bacteriophage therapy Lost to follow-up (n = 4) Lost to follow-up (n = 4) Patient died before 28 days Patient died before 28 days follow-up follow-up Analyzed (n = 34) Analyzed (n = 34) between group C and group B, with no statistically significant difference observed between th...</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>MEDICION</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>REPORTE</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>...sed on the previous study, “Biological therapy on infected from April 2024 to May 2025. The Institutional Ethics Committee traumatic wounds: A case-control study,” the sample size formula approved the study protocol. The clinical trial was registered with for two independent proportions is as follows:7 registration number CTRI/2024/03/064013. Patients admitted to the ICU were screened for eligibility. Inclusion criteria for patient (Z +Z )2 (p1q1+p2q2) selection were adults (age &gt; 18 years)...</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>...he sample size formula approved the study protocol. The clinical trial was registered with for two independent proportions is as follows:7 registration number CTRI/2024/03/064013. Patients admitted to the ICU were screened for eligibility. Inclusion criteria for patient (Z +Z )2 (p1q1+p2q2) selection were adults (age &gt; 18 years) admitted to the ICU following n= 1−α 1−β trauma, including head injury, spinal cord injury, or polytrauma, (p1−p2)2 who developed PUs (grade III–IV). Patients who refu...</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>...% of the interventional group) burns, or tuberculosis were excluded. The study procedure was p2 = 0.33 (representing a 2-point improvement in depth of explained to all eligible participants and their attendants. Written wound in 33% of the control group) informed consent was obtained from the patient or from the attendant if the patient was unable to consent. A total of 76 patients Z 1 − α = 1.96 at a 5% level of significance were screened for the study. Randomization was performed using...</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>...on. Our contributed to repeated infections and the development of PUs.24 findings on safety are consistent with this report. The limitation No prior study has evaluated bacteriophage therapy specifically of their study was the absence of a control group. In contrast, our for PUs. In comparison with previous studies conducted largely study was a randomized controlled trial with a control group, and in ambulatory or burn patients, our study uniquely evaluated ICU bacteriophage therapy was u...</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>...ion and the associated risk of driving antimicrobial resistance. Bacteriophage therapy, with its ability to target resistant and biofilm-associated bacteria, offers a potential “alternative.” We aimed to evaluate the efficacy and safety of topical bacteriophage therapy for the management of PUs in critically ill ICU patients and its comparison to conventional therapy. Patients and methods: This prospective, randomized, double-blind controlled trial was conducted in the ICU of a tert...</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>...care center between April 2024 and May 2025. Seventy-six adult patients with grade II–IV PUs were screened, and 68 were enrolled (34 in each group). Group C received conventional therapy, while group B received conventional plus customized topical bacteriophage therapy. Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool; tissue type, exudate amount, and ulcer dimensions were assessed at baseline and on days 5, 7, 14, 21, and 28. The primary objective was to...</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>...in group B (p &lt; 0.05). Group B also showed faster epithelialization, an earlier decrease in exudate, and more closed ulcers. These differences became statistically significant from day 7 onward. No adverse events were reported. Conclusion: Topical bacteriophage therapy is a safe and effective adjunct to conventional care in the management of PUs among ICU patients. Keywords: Antibiotics, Bacteriophages, Intensive care unit, Pressure ulcers, Trauma. Indian Journal of Critical Care Me...</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>CASO</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>...onal Therapy: A Randomized Controlled Trial. Indian J Crit Care Med 2026;30(3):196–203. Trauma is a modern-day epidemic, with a marked increase in the Source of support: Nil number of accidents due to the rapid growth of the motor industry Conflict of interest: None and economic expansion. Patients with head injuries, cervical spine trauma, and polytrauma require prolonged admission to the intensive care unit (ICU). Patients in an ICU are at a high risk of developing PUs because of severe trauma...</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>...conducted in the ICU of an apex care center in the Department Sample Size of Anaesthesiology and Microbiology. The study period was Based on the previous study, “Biological therapy on infected from April 2024 to May 2025. The Institutional Ethics Committee traumatic wounds: A case-control study,” the sample size formula approved the study protocol. The clinical trial was registered with for two independent proportions is as follows:7 registration number CTRI/2024/03/064013. Patients admitted...</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>EST-132</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>...entional group) burns, or tuberculosis were excluded. The study procedure was p2 = 0.33 (representing a 2-point improvement in depth of explained to all eligible participants and their attendants. Written wound in 33% of the control group) informed consent was obtained from the patient or from the attendant if the patient was unable to consent. A total of 76 patients Z 1 − α = 1.96 at a 5% level of significance were screened for the study. Randomization was performed using Z 1 − β = 1.282 at...</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>ALEATORIZACION</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>...the individual IND (investigational new All clinical isolates were grown from individual colonies in ly- drug) for each patient on a compassionate-use basis. Each pa- sogeny broth (LB) at 37°C. For plaque (phage) isolation from tient case was treated after approval from the local institutional environmental samples or TAILΦR’s library of phages, a review board (IRB). All patients provided informed consent for double-agar overlay assay was performed using the patient’s clinical use of p...</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>...ted but 4 weeks lat- noted, but mostly at low concentrations of antibiotic and was er the patient developed an infection caused by Peptoniphilus less apparent in the earlier time point. The physician was in- asaccharolyticus. This patient was treated with an antibiotic formed of this and decided to use ceftriaxone. and avoided hip disarticulation. For case 8 (LVAD; S. aureus), there were no complications; the patient cleared the initial bac- Clinical Outcomes terial infection without d...</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>...: Phage targeted cloacae 692, Enterobacter cloacae (SLC4). IV, 6 wk effects pathogen was eradicated. However, 693, Treatment: phage cocktail and later developed new infection due to 694 cefepime Peptoniphilus asaccharolyticus. The patient was treated successfully with oral amoxicillin-clavulanate and will remain on life-long suppression. E. cloacae was not recovered from any of the cultures at the time of recurrence. The treating physician believed the E. cloacae has been eradicated. A...</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>CEGAMIENTO</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>PERDIDAS</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>MEDICION</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>REPORTE</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>...acterials and Innovative Laboratories for Phage (Φ) Research; TEM, Transmission Electron Microscopy; Sub., Submission; Quant., Quantificaiton. The figure was created with BioRender.com. 1080 • CID 2023:77 (15 October) • Green et alTable 1. Inclusion Criteria for Phage Therapy Table 2. Cocktail Report Contents Antibiotic treatment has been ineffective Name and description of phages Multidrug-resistant organism (or difficult-to-treat infection) Manufacturer Chronically infected patienta Descript...</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>...as by our group but was based on a clinical profile provided by we improved efficiency over time (Supplementary Figure 1). the treating physicians. Of the 12 patient cases, more than 50% (7/12 cases) had a secondary immune deficiency. Ten Phage Cocktails Were Generated Against 6 Different Species TAILΦR had originally provided phages for 12 patients. For 1 case, we were not provided sufficient clinical information despite Mode of Administration treatment being regarded as successful, so w...</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>...s TAILΦR had originally provided phages for 12 patients. For 1 case, we were not provided sufficient clinical information despite Mode of Administration treatment being regarded as successful, so we omitted this case. All patients received concomitant antibiotic therapy. All pa- One patient was retreated with a different phage cocktail after de- tients were treated with intravenous (IV) phage therapy veloping a new infection (thus, 12 cases) (Tables 5and 6). The (Table 5). Four patient cases (33%)...</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>...ed concomitant intraoper- ing data, genomic analysis, and predicted lifestyle of each phage. ative phages. The fourth patient (case 12) received phages top- Based on a sequence analysis, all phages lacked known bacterial ically. All non-IV doses were single one-time applications. The virulence factors (eg, toxins) and antibiotic-resistance genes. average duration for IV treatment was 5.6 weeks. Two different methods were used to assess whether the phage ex- isted as temperate (in...</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>CASO</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>...ts with CF with lung infection. Terwilliger et al., 2022) and 12 (Figure 3). Of particular note is case 8 in which 2 antibiotics were tested (Figure 1Hi, Hii): ceftriaxone and cefazolin. For the phage cocktail with cefazolin, likely due to comorbidities of the patients. For example, in we observed antagonism. For ceftriaxone, antagonism was also case 2 (PJI; E. cloacae), E. cloacae was eradicated but 4 weeks lat- noted, but mostly at low concentrations of antibiotic and was er the pati...</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>...asis. Each pa- sogeny broth (LB) at 37°C. For plaque (phage) isolation from tient case was treated after approval from the local institutional environmental samples or TAILΦR’s library of phages, a review board (IRB). All patients provided informed consent for double-agar overlay assay was performed using the patient’s clinical use of phages and their data being used for research bacterial isolate as host. Individual plaques were serially pas- purposes and publication. The manufacturing inst...</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>...A. A. F. and K. L. W. provided phages for treat- All other authors report no potential conflicts. All authors have submit- ment and reviewed and edited the manuscript. A. L. T. organized phage ted the ICMJE Form for Disclosure of Potential Conflicts of Interest. therapy treatments; contributed to data collection, analysis, and interpreta- Conflicts that the editors consider relevant to the content of the manuscript tion; and reviewed and edited the manuscript. B. W. T. provided necessary have bee...</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>...atments; contributed to data collection, analysis, and interpreta- Conflicts that the editors consider relevant to the content of the manuscript tion; and reviewed and edited the manuscript. B. W. T. provided necessary have been disclosed. funding for the work at TAILOR and reviewed and provided edits for the manuscript. A. M. is the faculty founder and current Center Director of References TAILOR, analyzed and interpretated data, and wrote and edited the 1. World Health Organizatio...</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>ALEATORIZACION</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Secuencia de asignación y ocultamiento (RoB 2, dominio 1)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Desviaciones de la intervención asignada (RoB 2, dominio 2)</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>CEGAMIENTO</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Cegamiento de pacientes, personal y evaluadores (RoB 2 d.2 y d.4)</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>PERDIDAS</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Datos de desenlace faltantes (RoB 2, dominio 3)</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>MEDICION</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Medición del desenlace (RoB 2, dominio 4)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>REPORTE</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Selección del resultado informado y registro previo (RoB 2, dominio 5)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Confusión y selección de participantes (ROBINS-I, dominios 1 y 2)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>...ious studies have shown that the level of antiphage activity of sera (AAS) calculated as the rate of phage inactivation (K) in patients undergoing PT depends on several factors such as the route of phage administration, phage type, and the dose of the phage preparation (Figure 1) [6]. Oral and rectal administration of phages are considered the least immunogenic, whereas the combination of both local and oral administration is more immunogenic. Purified phage preparations with hig...</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>...age preparation (Figure 1) [6]. Oral and rectal administration of phages are considered the least immunogenic, whereas the combination of both local and oral administration is more immunogenic. Purified phage preparations with higher phage titer may be more Antibiotics2025,14,87 immunogenic in comparison to phage lysates [6]. The correlation between the h2igohf1e0r phage titer and the higher antibody level is not a rule, and the degree of phage purification may also play an essent...</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Clasificación de la intervención y su medición (ROBINS-I, d.3 y d.6)</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>...is not a rule, and the degree of phage purification may also play an essential part. Żaczek et al. [7] showed that sometimes lysates are more Ourpreviousstudieshaveshownthatthelevelofantiphageactivityofsera(AAS) immunogenic (despite lower titers) than purified preparations, which was explained by calculated as the rate of phage inactivation (K) in patients undergoing PT depends on the influence of impurities on the higher antibody levels. Antibody responses to phage severalfactor...</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>CASO</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Descripción del caso: demografía, historia, diagnóstico, seguimiento (JBI)</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>CONFLICTOS</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Financiación, conflictos de interés y consentimiento</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>...therapy,R.M.;resources, M.Ł.-S.andA.G.;writing—originaldraftpreparation,M.Ł.-S.,B.W.-D.andA.G.;writing—review&amp; editing,M.Ł.-S.,M.Z˙.andA.G.;supervision,A.G.,M.Ł.-S.andB.W.-D.Allauthorshavereadand agreedtothepublishedversionofthemanuscript. Funding:ThisworkwassupportedbyinstitutionalfundsfromtheHirszfeldInstituteofImmunology andExperimentalTherapyofthePolishAcademyofSciences. InstitutionalReviewBoardStatement: ThestudywasconductedbytheDeclarationofHelsinki, andapprovedbytheBioethicsC...</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Sesgo por confusión</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>"When phage therapy was initiated, all patients were concurrently on IV antibiotics (n = 6) or recently completed antibiotics (n = 3)." || Nota: No hubo asignación comparativa ni ajuste por gravedad basal, tratamientos concomitantes o diferencias clínicas; el efecto de la fagoterapia no puede separarse de cointervenciones ni pronóstico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>CONFUSION</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección de los participantes</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>"Individuals were selected for treatment owing to a combination of the following: lack of clinical response to antibiotics, persistent symptoms and/or clinical decline despite comprehensive CF care, severity of pulmonary exacerbations, and no additional approved therapeutics available." || Nota: Selección clínica por compasión y gravedad; no se describe muestreo consecutivo ni una población fuente comparable. El brazo A es además una serie de casos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>"Phage therapy was personalized on the basis of susceptibility of the PsA sputum isolates to phages in the phage library." || Nota: La intervención se define y verifica mediante susceptibilidad del aislado; no obstante, hubo single-phage y cócteles, con dosis/frecuencias y nebulizadores no idénticos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>DESVIACIONES</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>"Across the cohort, there were differences in the number of phages used (for example, single versus cocktail), duration of phage therapy (7-10 days) and frequency of treatment (inpatient and outpatient)." || Nota: La intervención y la administración variaron entre participantes y no existió comparador; las desviaciones y cointervenciones impiden interpretar una comparación interna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>PERDIDAS</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Sesgo por datos faltantes</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>"Sputum samples were collected at different intervals over the subsequent 28 days ... and spirometry was performed after phage therapy (21-30 days) at each patient's CF center." || Nota: Los tiempos de recogida variaron; además, el seguimiento de eventos adversos dependió del reporte de pacientes/equipos y no hubo cuestionarios estandarizados ni comité de seguridad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>MEDICION</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Sesgo en la medición de los desenlaces</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>"Because each case was a SPIND, standardized CF symptom diaries or questionnaires were not used and there was no safety monitoring board." || Nota: No se describe un protocolo prospectivo de resultados ni registro de desenlaces; se presentan varios análisis microbiológicos, clínicos y fenotípicos sin una jerarquía clara de selección del resultado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>REPORTE</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección del resultado notificado</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>"Here, we present outcomes from the first nine adult pwCF compassionate cases who were treated with nebulized phage(s) using the above approach." || Nota: Serie consecutiva de casos compasivos, sin comparador y con múltiples desenlaces; no se identifica un plan de análisis preespecificado que permita descartar selección del resultado reportado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>EST-004</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Juicio global del estudio</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
           <t>"Because of the nature of compassionate phage therapy, there was no control group for comparison." || Nota: Juicio global: el peor dominio es grave y la ausencia de control, junto con confusión por indicación y selección clínica, compromete la inferencia comparativa. Se trata de una evaluación adaptada basada en ROBINS-I porque el artículo no presenta una cohorte comparativa independiente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E230"/>
+  <autoFilter ref="A1:E175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>Dominio</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>Dominio</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">

--- a/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
+++ b/verificables revisión sistemática/S18b_frases_cosechadas_por_tema.xlsx
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
